--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487422_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487422_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0279</v>
+        <v>4.7</v>
       </c>
       <c r="E2" t="n">
-        <v>2.784</v>
+        <v>3.2957</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2439</v>
+        <v>1.4043</v>
       </c>
       <c r="G2" t="n">
         <v>1.4927</v>
@@ -610,13 +610,13 @@
         <v>0.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.7372</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2023</v>
+        <v>0.3094</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2675</v>
+        <v>0.4279</v>
       </c>
       <c r="V2" t="n">
         <v>1.8825</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. MASEDA SOILAN</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2065</v>
+        <v>2.3312</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.4389</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2181</v>
+        <v>1.8923</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9591</v>
+        <v>1.9007</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4285</v>
+        <v>0.996</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5306</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0471</v>
+        <v>2.0934</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7245</v>
+        <v>2.0126</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6774</v>
+        <v>0.0808</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0062</v>
+        <v>-0.1927</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.153</v>
+        <v>-1.0166</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1468</v>
+        <v>0.8239</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -688,28 +688,28 @@
         <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2819</v>
+        <v>1.0964</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4286</v>
+        <v>0.107</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8533</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8837</v>
+        <v>-0.6659</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8837</v>
+        <v>-0.3905</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>Á. SONEIRA BOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2556</v>
+        <v>2.2328</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3366</v>
+        <v>2.0428</v>
       </c>
       <c r="F4" t="n">
-        <v>1.919</v>
+        <v>0.1901</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9007</v>
+        <v>2.7776</v>
       </c>
       <c r="H4" t="n">
-        <v>0.996</v>
+        <v>-1.7492</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9046999999999999</v>
+        <v>4.5269</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0934</v>
+        <v>2.9037</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0126</v>
+        <v>-0.9358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0808</v>
+        <v>3.8394</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1927</v>
+        <v>-0.1261</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0166</v>
+        <v>-0.8135</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8239</v>
+        <v>0.6874</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.3709</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0208</v>
+        <v>0.8676</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0047</v>
+        <v>0.2347</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0161</v>
+        <v>0.633</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6659</v>
+        <v>-1.2166</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3905</v>
+        <v>0.2754</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9771</v>
+        <v>2.1108</v>
       </c>
       <c r="E5" t="n">
         <v>2.1754</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1983</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>1.6745</v>
@@ -844,13 +844,13 @@
         <v>0.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0891</v>
+        <v>0.0446</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0891</v>
+        <v>0.2228</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Á. SONEIRA BOO</t>
+          <t>D. MASEDA SOILAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6793</v>
+        <v>2.0624</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6763</v>
+        <v>0.2721</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0029</v>
+        <v>1.7904</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7776</v>
+        <v>-0.9591</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7492</v>
+        <v>-0.4285</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5269</v>
+        <v>-0.5306</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9037</v>
+        <v>0.0471</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9358</v>
+        <v>0.7245</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8394</v>
+        <v>-0.6774</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1261</v>
+        <v>-1.0062</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8135</v>
+        <v>-1.153</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6874</v>
+        <v>0.1468</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.3709</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3141</v>
+        <v>2.1379</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1317</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4459</v>
+        <v>1.4256</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2166</v>
+        <v>0.8837</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2754</v>
+        <v>0.8837</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0367</v>
+        <v>1.1879</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.899</v>
+        <v>-1.6943</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9357</v>
+        <v>2.8822</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0075</v>
@@ -1000,13 +1000,13 @@
         <v>1.5668</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1812</v>
+        <v>1.3324</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1141</v>
+        <v>0.0906</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2953</v>
+        <v>1.2419</v>
       </c>
       <c r="V7" t="n">
         <v>0.8837</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5556</v>
+        <v>0.1568</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1197</v>
+        <v>-0.572</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6753</v>
+        <v>0.7288</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8445</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4001</v>
+        <v>1.0013</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2039</v>
+        <v>0.7516</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1962</v>
+        <v>0.2497</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ BLANCO</t>
+          <t>H. SANCHEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.5453</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8988</v>
+        <v>-0.8219</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2167</v>
+        <v>0.2766</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1745</v>
+        <v>-0.5335</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4526</v>
+        <v>-1.1497</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2781</v>
+        <v>0.6162</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0464</v>
+        <v>0.0717</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0464</v>
+        <v>-0.5393</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1281</v>
+        <v>-0.6052</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4062</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2781</v>
+        <v>0.0052</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1958</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1958</v>
+        <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6884</v>
+        <v>0.3383</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3435</v>
+        <v>-0.1517</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3449</v>
+        <v>0.4901</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. SANCHEZ EXPOSITO</t>
+          <t>M. RODRÍGUEZ BLANCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8302</v>
+        <v>-0.5737</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0266</v>
+        <v>-0.737</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1964</v>
+        <v>0.1633</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5335</v>
+        <v>-1.1745</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1497</v>
+        <v>-1.4526</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6162</v>
+        <v>0.2781</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0717</v>
+        <v>-1.0464</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5393</v>
+        <v>-1.0464</v>
       </c>
       <c r="L10" t="n">
-        <v>0.611</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6052</v>
+        <v>-0.1281</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.4062</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0052</v>
+        <v>0.2781</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5668</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9585</v>
+        <v>-0.1958</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0535</v>
+        <v>0.7966</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3564</v>
+        <v>0.5052</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4099</v>
+        <v>0.2914</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. CAMBON DOMINGUEZ</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9061</v>
+        <v>-0.9083</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3625</v>
+        <v>-1.7606</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4564</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1642</v>
+        <v>-0.8552</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6581</v>
+        <v>0.014</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5061</v>
+        <v>-0.8691</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0164</v>
+        <v>-0.3208</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0957</v>
+        <v>0.9628</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9206</v>
+        <v>-1.2836</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1479</v>
+        <v>-0.5344</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5624</v>
+        <v>-0.9489</v>
       </c>
       <c r="O11" t="n">
         <v>0.4145</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7834</v>
+        <v>-2.546</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1751</v>
+        <v>-3.1336</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2754</v>
+        <v>0.7256</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7287</v>
+        <v>-0.0735</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5467</v>
+        <v>0.7991</v>
       </c>
       <c r="V11" t="n">
-        <v>2.7662</v>
+        <v>1.7673</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1003</v>
+        <v>1.7673</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>M. CAMBON DOMINGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9638</v>
+        <v>-1.0201</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9561</v>
+        <v>-1.6101</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9923</v>
+        <v>0.5901</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1657</v>
+        <v>-4.1642</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2521</v>
+        <v>-2.6581</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0864</v>
+        <v>-1.5061</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1564</v>
+        <v>-3.0164</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2825</v>
+        <v>-1.0957</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1261</v>
+        <v>-1.9206</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0093</v>
+        <v>-1.1479</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.9696</v>
+        <v>-1.5624</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9603</v>
+        <v>0.4145</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5668</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3502</v>
+        <v>-1.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7688</v>
+        <v>1.1614</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5505</v>
+        <v>0.4811</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2183</v>
+        <v>0.6803</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>2.7662</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.1003</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3489</v>
+        <v>-1.4298</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0676</v>
+        <v>-2.1014</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7187</v>
+        <v>0.6716</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8552</v>
+        <v>-1.1657</v>
       </c>
       <c r="H13" t="n">
-        <v>0.014</v>
+        <v>-2.2521</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8691</v>
+        <v>1.0864</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3208</v>
+        <v>-0.1564</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9628</v>
+        <v>-0.2825</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2836</v>
+        <v>0.1261</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5344</v>
+        <v>-1.0093</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9489</v>
+        <v>-1.9696</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4145</v>
+        <v>0.9603</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.546</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.1336</v>
+        <v>-2.3502</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>0.285</v>
+        <v>1.3027</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3805</v>
+        <v>0.4052</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6655</v>
+        <v>0.8975</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7673</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7673</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.0077</v>
+        <v>10.3047</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.3696</v>
+        <v>-1.0724</v>
       </c>
       <c r="F14" t="n">
-        <v>11.3771</v>
+        <v>11.3773</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.8587</v>
+        <v>-3.858700000000001</v>
       </c>
       <c r="H14" t="n">
         <v>-13.28</v>
@@ -1519,10 +1519,10 @@
         <v>9.4215</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8234</v>
+        <v>1.823400000000002</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.4061</v>
+        <v>-1.406100000000001</v>
       </c>
       <c r="L14" t="n">
         <v>3.2295</v>
@@ -1546,10 +1546,10 @@
         <v>8.8131</v>
       </c>
       <c r="S14" t="n">
-        <v>11.2453</v>
+        <v>11.542</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8967</v>
+        <v>3.1936</v>
       </c>
       <c r="U14" t="n">
         <v>8.348700000000001</v>
@@ -1558,7 +1558,7 @@
         <v>7.5175</v>
       </c>
       <c r="W14" t="n">
-        <v>7.620099999999999</v>
+        <v>7.6201</v>
       </c>
       <c r="X14" t="n">
         <v>-0.1026999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7973</v>
+        <v>3.3551</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7142</v>
+        <v>1.9189</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0831</v>
+        <v>1.4362</v>
       </c>
       <c r="G15" t="n">
         <v>4.4648</v>
@@ -1624,13 +1624,13 @@
         <v>2.7419</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.4508</v>
+        <v>-1.8931</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.8415</v>
+        <v>-1.6368</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.2563</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6571</v>
+        <v>1.706</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2525</v>
+        <v>-1.5595</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9096</v>
+        <v>3.2655</v>
       </c>
       <c r="G16" t="n">
         <v>2.6881</v>
@@ -1702,13 +1702,13 @@
         <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6554</v>
+        <v>-1.6065</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.981</v>
+        <v>-1.288</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6743</v>
+        <v>-0.3185</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5507</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3333</v>
+        <v>0.8381</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7802</v>
+        <v>0.9616</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.447</v>
+        <v>-0.1234</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2537</v>
@@ -1780,13 +1780,13 @@
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0005</v>
+        <v>-0.4957</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8299</v>
+        <v>0.0112</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8304</v>
+        <v>-0.5068</v>
       </c>
       <c r="V17" t="n">
         <v>0.6083</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2604</v>
+        <v>-1.1581</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6855</v>
+        <v>-1.5831</v>
       </c>
       <c r="F18" t="n">
         <v>0.425</v>
@@ -1858,10 +1858,10 @@
         <v>0.9792</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-0.7581</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8316</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="U18" t="n">
         <v>-0.0288</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5627</v>
+        <v>-2.1671</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.0257</v>
+        <v>-4.7187</v>
       </c>
       <c r="F19" t="n">
-        <v>2.463</v>
+        <v>2.5516</v>
       </c>
       <c r="G19" t="n">
         <v>0.4015</v>
@@ -1936,13 +1936,13 @@
         <v>2.1543</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.2188</v>
+        <v>-1.8232</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.9603</v>
+        <v>-1.6533</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2585</v>
+        <v>-0.17</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9412</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6314</v>
+        <v>-3.3364</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7794</v>
+        <v>-0.677</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8521</v>
+        <v>-2.6594</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7911</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8369</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1286</v>
+        <v>-1.0263</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2918</v>
+        <v>0.4845</v>
       </c>
       <c r="V20" t="n">
         <v>-3.3745</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0896</v>
+        <v>-3.3715</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3417</v>
+        <v>-3.137</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7479</v>
+        <v>-0.2344</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6006</v>
@@ -2092,13 +2092,13 @@
         <v>1.7626</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7805</v>
+        <v>-1.0623</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0098</v>
+        <v>-0.8052</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7706</v>
+        <v>-0.2572</v>
       </c>
       <c r="V21" t="n">
         <v>-1.492</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2512</v>
+        <v>-3.8271</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7868</v>
+        <v>-2.5822</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4643</v>
+        <v>-1.2449</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3173</v>
@@ -2170,13 +2170,13 @@
         <v>1.5668</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4419</v>
+        <v>-1.0178</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4256</v>
+        <v>-1.221</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0162</v>
+        <v>0.2032</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1003</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.0076</v>
+        <v>-7.961000000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.3772</v>
+        <v>-11.377</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3694</v>
+        <v>3.416199999999999</v>
       </c>
       <c r="G23" t="n">
         <v>3.8588</v>
@@ -2248,13 +2248,13 @@
         <v>13.7092</v>
       </c>
       <c r="S23" t="n">
-        <v>-11.2452</v>
+        <v>-9.198499999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-8.3485</v>
+        <v>-8.348700000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.8964</v>
+        <v>-0.8499000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-7.517499999999999</v>
